--- a/results_(stress_test)_baselines_cross_valid/cnn_evaluation(stress_test)_pcc_origin.xlsx
+++ b/results_(stress_test)_baselines_cross_valid/cnn_evaluation(stress_test)_pcc_origin.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\RnD_Repo\Research_Engineeirng\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_original\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\RnD_Repo\Research_Engineering\feature_fusion_PCCxSigmoid-PLV-\results_(stress_test)_baselines_cross_valid\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B542D2A-C105-43F7-9536-103E68E0BCFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nrn_62" sheetId="1" r:id="rId1"/>
@@ -236,22 +236,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -1127,189 +1119,189 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A2" s="3">
+      <c r="A2">
         <v>92.97270449283009</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>92.485449200300948</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2">
         <v>0.2160732091363366</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2">
         <v>92.97270449283009</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A3" s="3">
+      <c r="A3">
         <v>3.6723191410127392</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3">
         <v>4.0542209595909764</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3">
         <v>0.13702199928380979</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3">
         <v>3.6723191410127378</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A4" s="3">
+      <c r="A4">
         <v>92.656851126163161</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>92.185357970009463</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4">
         <v>0.2360180365622819</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4">
         <v>92.656851126163161</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A5" s="3">
+      <c r="A5">
         <v>3.8557140126956959</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>4.1862833242412467</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5">
         <v>0.1533813601961018</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5">
         <v>3.8557140126956959</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A6" s="3">
+      <c r="A6">
         <v>90.612485113769722</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>90.049361274020285</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <v>0.29389272846527909</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6">
         <v>90.612485113769722</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A7" s="3">
+      <c r="A7">
         <v>4.1717853309388913</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>4.5232246954320994</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7">
         <v>0.1502635086941152</v>
       </c>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>4.1717853309388939</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="E7" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A8" s="3">
+      <c r="A8">
         <v>76.890048068466555</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>76.424179894802663</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <v>0.58794236976228897</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8">
         <v>76.890048068466555</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E8" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A9" s="3">
+      <c r="A9">
         <v>8.1206319222896362</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>8.3692490038067824</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9">
         <v>0.1938864939121652</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9">
         <v>8.1206319222896362</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="E9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A10" s="3">
+      <c r="A10">
         <v>57.431157132270449</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>55.817166373785298</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10">
         <v>0.99866620260497752</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10">
         <v>57.431157132270457</v>
       </c>
-      <c r="E10" s="3" t="s">
+      <c r="E10" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A11" s="3">
+      <c r="A11">
         <v>8.7326493747450371</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11">
         <v>9.4522568492704835</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11">
         <v>0.1892415083873272</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11">
         <v>8.7326493747450353</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1325,158 +1317,158 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="1" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A2" s="4">
+      <c r="A2">
         <v>92.97270449283009</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2">
         <v>3.6723191410127392</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2">
         <v>92.485449200300948</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2">
         <v>4.0542209595909764</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2">
         <v>92.97270449283009</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2">
         <v>3.6723191410127378</v>
       </c>
-      <c r="G2" s="4">
+      <c r="G2">
         <v>0.2160732091363366</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2">
         <v>0.13702199928380979</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A3" s="4">
+      <c r="A3">
         <v>92.656851126163161</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3">
         <v>3.8557140126956959</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3">
         <v>92.185357970009463</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D3">
         <v>4.1862833242412467</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3">
         <v>92.656851126163161</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3">
         <v>3.8557140126956959</v>
       </c>
-      <c r="G3" s="4">
+      <c r="G3">
         <v>0.2360180365622819</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3">
         <v>0.1533813601961018</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A4" s="4">
+      <c r="A4">
         <v>90.612485113769722</v>
       </c>
-      <c r="B4" s="4">
+      <c r="B4">
         <v>4.1717853309388913</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4">
         <v>90.049361274020285</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4">
         <v>4.5232246954320994</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4">
         <v>90.612485113769722</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4">
         <v>4.1717853309388939</v>
       </c>
-      <c r="G4" s="4">
+      <c r="G4">
         <v>0.29389272846527909</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4">
         <v>0.1502635086941152</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A5" s="4">
+      <c r="A5">
         <v>76.890048068466555</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>8.1206319222896362</v>
       </c>
-      <c r="C5" s="4">
+      <c r="C5">
         <v>76.424179894802663</v>
       </c>
-      <c r="D5" s="4">
+      <c r="D5">
         <v>8.3692490038067824</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5">
         <v>76.890048068466555</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5">
         <v>8.1206319222896362</v>
       </c>
-      <c r="G5" s="4">
+      <c r="G5">
         <v>0.58794236976228897</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5">
         <v>0.1938864939121652</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
-      <c r="A6" s="4">
+      <c r="A6">
         <v>57.431157132270449</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>8.7326493747450371</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>55.817166373785298</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6">
         <v>9.4522568492704835</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6">
         <v>57.431157132270457</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6">
         <v>8.7326493747450353</v>
       </c>
-      <c r="G6" s="4">
+      <c r="G6">
         <v>0.99866620260497752</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6">
         <v>0.1892415083873272</v>
       </c>
     </row>
